--- a/empresas/gnlink/analises-financeiras/bp/gnlink-bp-historico.xlsx
+++ b/empresas/gnlink/analises-financeiras/bp/gnlink-bp-historico.xlsx
@@ -14,6 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overrides" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VolumeHist" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fatores" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preco" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IdxMacro" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReceitaHist" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3324,6 +3327,2660 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:GL13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>planta</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>produto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2027-04</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2027-05</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2027-06</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>2027-07</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>2027-08</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>2027-09</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>2027-11</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>2028-01</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>2028-02</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>2028-04</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>2028-06</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>2028-08</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>2028-09</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>2028-10</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>2028-11</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>2028-12</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>2029-01</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>2029-02</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>2029-03</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>2029-04</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>2029-05</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>2029-06</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>2029-07</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>2029-08</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>2029-09</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>2029-10</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>2029-11</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>2029-12</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>2030-01</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>2030-02</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>2030-03</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>2030-04</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>2030-05</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>2030-06</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>2030-07</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>2030-08</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>2030-09</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>2030-10</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>2030-11</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>2030-12</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>2031-01</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>2031-02</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>2031-03</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>2031-04</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>2031-05</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>2031-06</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>2031-07</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>2031-08</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>2031-09</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>2031-10</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>2031-11</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>2031-12</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>2032-01</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>2032-02</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>2032-03</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>2032-04</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>2032-05</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>2032-06</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>2032-07</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>2032-08</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>2032-09</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>2032-10</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>2032-11</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>2032-12</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>2033-01</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>2033-02</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>2033-03</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>2033-04</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>2033-05</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>2033-06</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>2033-07</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>2033-08</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>2033-09</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>2033-10</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>2033-11</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>2033-12</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>2034-01</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>2034-02</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>2034-03</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>2034-04</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>2034-05</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>2034-06</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>2034-07</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>2034-08</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>2034-09</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>2034-10</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>2034-11</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>2035-01</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>2035-02</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>2035-03</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>2035-04</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>2035-05</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>2035-06</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>2035-07</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>2035-08</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>2035-09</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>2035-10</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>2035-11</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>2035-12</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>2036-01</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>2036-02</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>2036-03</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>2036-04</t>
+        </is>
+      </c>
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>2036-05</t>
+        </is>
+      </c>
+      <c r="FH1" t="inlineStr">
+        <is>
+          <t>2036-06</t>
+        </is>
+      </c>
+      <c r="FI1" t="inlineStr">
+        <is>
+          <t>2036-07</t>
+        </is>
+      </c>
+      <c r="FJ1" t="inlineStr">
+        <is>
+          <t>2036-08</t>
+        </is>
+      </c>
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>2036-09</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
+        <is>
+          <t>2036-10</t>
+        </is>
+      </c>
+      <c r="FM1" t="inlineStr">
+        <is>
+          <t>2036-11</t>
+        </is>
+      </c>
+      <c r="FN1" t="inlineStr">
+        <is>
+          <t>2036-12</t>
+        </is>
+      </c>
+      <c r="FO1" t="inlineStr">
+        <is>
+          <t>2037-01</t>
+        </is>
+      </c>
+      <c r="FP1" t="inlineStr">
+        <is>
+          <t>2037-02</t>
+        </is>
+      </c>
+      <c r="FQ1" t="inlineStr">
+        <is>
+          <t>2037-03</t>
+        </is>
+      </c>
+      <c r="FR1" t="inlineStr">
+        <is>
+          <t>2037-04</t>
+        </is>
+      </c>
+      <c r="FS1" t="inlineStr">
+        <is>
+          <t>2037-05</t>
+        </is>
+      </c>
+      <c r="FT1" t="inlineStr">
+        <is>
+          <t>2037-06</t>
+        </is>
+      </c>
+      <c r="FU1" t="inlineStr">
+        <is>
+          <t>2037-07</t>
+        </is>
+      </c>
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t>2037-08</t>
+        </is>
+      </c>
+      <c r="FW1" t="inlineStr">
+        <is>
+          <t>2037-09</t>
+        </is>
+      </c>
+      <c r="FX1" t="inlineStr">
+        <is>
+          <t>2037-10</t>
+        </is>
+      </c>
+      <c r="FY1" t="inlineStr">
+        <is>
+          <t>2037-11</t>
+        </is>
+      </c>
+      <c r="FZ1" t="inlineStr">
+        <is>
+          <t>2037-12</t>
+        </is>
+      </c>
+      <c r="GA1" t="inlineStr">
+        <is>
+          <t>2038-01</t>
+        </is>
+      </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>2038-02</t>
+        </is>
+      </c>
+      <c r="GC1" t="inlineStr">
+        <is>
+          <t>2038-03</t>
+        </is>
+      </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t>2038-04</t>
+        </is>
+      </c>
+      <c r="GE1" t="inlineStr">
+        <is>
+          <t>2038-05</t>
+        </is>
+      </c>
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>2038-06</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>2038-07</t>
+        </is>
+      </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t>2038-08</t>
+        </is>
+      </c>
+      <c r="GI1" t="inlineStr">
+        <is>
+          <t>2038-09</t>
+        </is>
+      </c>
+      <c r="GJ1" t="inlineStr">
+        <is>
+          <t>2038-10</t>
+        </is>
+      </c>
+      <c r="GK1" t="inlineStr">
+        <is>
+          <t>2038-11</t>
+        </is>
+      </c>
+      <c r="GL1" t="inlineStr">
+        <is>
+          <t>2038-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GNC</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>23122.4526</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>13815.78</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>15542.7525</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>15048.61875</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>56578.314375</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>234859.7204204625</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>219736.26988192</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>152927.156423811</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>117778.933076805</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>122150.702998093</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>80911.73457790499</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>122507.315369736</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>57810.90488018999</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>99462.99509915954</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>149528.24294241</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>112541.3807193</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>68028.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>124481.8154062593</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GNL</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>684918.15</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2093995.33</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1606174.93905</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>292690.974675</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>217464.951</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>144667.514</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>604892.9728336898</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>285555.4383</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>432898.0367250001</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>538486.9906393349</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>365984.3439464998</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>964896.7388048647</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>664464.3417081152</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-39595.01968295805</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1406682.407670433</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>133966.9468129014</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>326752.6389999998</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>216639.9579999996</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>875415.6260000002</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2953129.237839999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3093447.053526719</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GNC</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>213104.7604988875</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>371012.5439415054</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>53653.12922469721</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GNL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>139686.162</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>462148.368</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>528734.2656749999</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>644859.0415426595</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>406923.272146545</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>800954.7191026192</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>708872.6800084645</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>452439.5242763074</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-58415.81741502541</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>970371.6786046007</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>788335.0688289392</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1173392.361211574</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1662079.252735665</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1545687.932420311</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1274867.022354955</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1845018.494604622</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GNC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>23102.85999999998</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>133591.764</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>136325.1062946302</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>69398.99849999999</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>135277.428030822</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GNL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1025610.47001</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1092358.193426715</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1226215.756832517</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1310316.656699226</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>858556.305239754</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GNC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GNL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GNC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GNL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GNC</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GNL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -28879,6 +31536,7201 @@
       </c>
       <c r="GL13" t="n">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F144"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>precoBase</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dataBase</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>indicador</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>residual</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>correcao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.847</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3.847</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.1649</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4.1649</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.9358</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3.9358</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.2085</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3.2085</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.4722</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4.4722</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.2085</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3.2085</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3.4155</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3.4155</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.2028</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1.1079</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4.1142</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2.0193</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3.269</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1.1741</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.79655378630096</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.29834621369904</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3.059</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9641000000000002</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3.84701592</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1.75211592</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.9707</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1.8758</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.2948999999999999</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1.7451</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1.8051</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3.2085</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1.1136</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3.2085</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1.1136</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3.341</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1.2461</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3.8232</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1.7283</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4.1142</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2.0193</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1.9551</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2.2551</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3.7297</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1.6348</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Brent Bahia</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3.7581</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2.138162186153062</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.430062186153062</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3.7297</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2.109762186153062</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2.080062186153063</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1.880062186153062</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4.0903</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2.470362186153062</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1.880062186153062</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>3.7189</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2.098962186153062</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3.172</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1.552062186153062</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1.880062186153062</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.2800621861530621</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Brent RN</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.5300621861530621</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>3.35685</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>3.35685</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>3.35685</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>3.35685</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>3.35685</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>3.35685</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>IPCA 100%</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>1.955625737850021</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>3.7589</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>1.514525737850021</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>3.7189</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1.474525737850021</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>3.7297</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>1.485325737850021</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>3.7189</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>1.474525737850021</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1.955625737850021</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Brent Sal</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:GK6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2027-04</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2027-05</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2027-06</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2027-07</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>2027-08</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>2027-09</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>2027-11</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>2028-01</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>2028-02</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>2028-04</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>2028-06</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>2028-08</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>2028-09</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>2028-10</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>2028-11</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>2028-12</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>2029-01</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>2029-02</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>2029-03</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>2029-04</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>2029-05</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>2029-06</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>2029-07</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>2029-08</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>2029-09</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>2029-10</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>2029-11</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>2029-12</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>2030-01</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>2030-02</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>2030-03</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>2030-04</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>2030-05</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>2030-06</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>2030-07</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>2030-08</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>2030-09</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>2030-10</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>2030-11</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>2030-12</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>2031-01</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>2031-02</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>2031-03</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>2031-04</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>2031-05</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>2031-06</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>2031-07</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>2031-08</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>2031-09</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>2031-10</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>2031-11</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>2031-12</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>2032-01</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>2032-02</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>2032-03</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>2032-04</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>2032-05</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>2032-06</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>2032-07</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>2032-08</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>2032-09</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>2032-10</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>2032-11</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>2032-12</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>2033-01</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>2033-02</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>2033-03</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>2033-04</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>2033-05</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>2033-06</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>2033-07</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>2033-08</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>2033-09</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>2033-10</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>2033-11</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>2033-12</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>2034-01</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>2034-02</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>2034-03</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>2034-04</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>2034-05</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>2034-06</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>2034-07</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>2034-08</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>2034-09</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>2034-10</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>2034-11</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>2035-01</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>2035-02</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>2035-03</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>2035-04</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>2035-05</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>2035-06</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>2035-07</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>2035-08</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>2035-09</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>2035-10</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>2035-11</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>2035-12</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>2036-01</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>2036-02</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>2036-03</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>2036-04</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>2036-05</t>
+        </is>
+      </c>
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>2036-06</t>
+        </is>
+      </c>
+      <c r="FH1" t="inlineStr">
+        <is>
+          <t>2036-07</t>
+        </is>
+      </c>
+      <c r="FI1" t="inlineStr">
+        <is>
+          <t>2036-08</t>
+        </is>
+      </c>
+      <c r="FJ1" t="inlineStr">
+        <is>
+          <t>2036-09</t>
+        </is>
+      </c>
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>2036-10</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
+        <is>
+          <t>2036-11</t>
+        </is>
+      </c>
+      <c r="FM1" t="inlineStr">
+        <is>
+          <t>2036-12</t>
+        </is>
+      </c>
+      <c r="FN1" t="inlineStr">
+        <is>
+          <t>2037-01</t>
+        </is>
+      </c>
+      <c r="FO1" t="inlineStr">
+        <is>
+          <t>2037-02</t>
+        </is>
+      </c>
+      <c r="FP1" t="inlineStr">
+        <is>
+          <t>2037-03</t>
+        </is>
+      </c>
+      <c r="FQ1" t="inlineStr">
+        <is>
+          <t>2037-04</t>
+        </is>
+      </c>
+      <c r="FR1" t="inlineStr">
+        <is>
+          <t>2037-05</t>
+        </is>
+      </c>
+      <c r="FS1" t="inlineStr">
+        <is>
+          <t>2037-06</t>
+        </is>
+      </c>
+      <c r="FT1" t="inlineStr">
+        <is>
+          <t>2037-07</t>
+        </is>
+      </c>
+      <c r="FU1" t="inlineStr">
+        <is>
+          <t>2037-08</t>
+        </is>
+      </c>
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t>2037-09</t>
+        </is>
+      </c>
+      <c r="FW1" t="inlineStr">
+        <is>
+          <t>2037-10</t>
+        </is>
+      </c>
+      <c r="FX1" t="inlineStr">
+        <is>
+          <t>2037-11</t>
+        </is>
+      </c>
+      <c r="FY1" t="inlineStr">
+        <is>
+          <t>2037-12</t>
+        </is>
+      </c>
+      <c r="FZ1" t="inlineStr">
+        <is>
+          <t>2038-01</t>
+        </is>
+      </c>
+      <c r="GA1" t="inlineStr">
+        <is>
+          <t>2038-02</t>
+        </is>
+      </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>2038-03</t>
+        </is>
+      </c>
+      <c r="GC1" t="inlineStr">
+        <is>
+          <t>2038-04</t>
+        </is>
+      </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t>2038-05</t>
+        </is>
+      </c>
+      <c r="GE1" t="inlineStr">
+        <is>
+          <t>2038-06</t>
+        </is>
+      </c>
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>2038-07</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>2038-08</t>
+        </is>
+      </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t>2038-09</t>
+        </is>
+      </c>
+      <c r="GI1" t="inlineStr">
+        <is>
+          <t>2038-10</t>
+        </is>
+      </c>
+      <c r="GJ1" t="inlineStr">
+        <is>
+          <t>2038-11</t>
+        </is>
+      </c>
+      <c r="GK1" t="inlineStr">
+        <is>
+          <t>2038-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ipca_m</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.008799806409606648</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.005800352549798493</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.0007004365967666626</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.005572743842739878</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.00240807218729634</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.0030492335</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.002504452</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.003810305</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.002818786788739512</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.00395</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.003109307691158517</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.00295</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.003366666666666667</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.002984327670453426</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.002766666666666667</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.002666666666666667</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.003353288279525641</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.002266666666666666</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.003125</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.002951539506995873</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.002962463596825057</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.002625</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.003170428845685722</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.002125</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.003083333333333333</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.002799706074858974</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.002683333333333334</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.002683333333333334</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.003081780872891523</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.003080233333333334</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.002796889702117448</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.002680633333333334</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.002680633333333334</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.003078682425351965</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.002081233333333333</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.0029938031</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.00271074281241533</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.0025946027</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.0025946027</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0.002992253742926613</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.0019958021</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.0029907092969</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.002707932069602915</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.0025919080973</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.0025919080973</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.002989161489183686</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.0019937062979</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.0029876185876031</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.002705124137533312</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.0025892161892027</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.0025892161892027</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0.002986072327694502</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.0019916125916021</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>0.002870898719076642</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ipca12</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04621113930566789</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.04506637430692439</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.04496273821268559</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.03925596126881703</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.03688016491565316</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.0392595167856582</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.04227578239682583</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.04498245142821999</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.04237599016056492</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.04424740127395888</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.04758099233947855</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0487301138907088</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.04831295791859591</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.04559874392677332</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.05057630414778758</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.05477189641674851</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.0552972858849774</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.05319635559255276</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.0535116523759851</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.05225222422012621</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05130500777503921</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.05172368758697643</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.04680811347037062</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.04461835648432833</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.04264384904568952</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.0444135121281346</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.03812496961112588</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.04142827006034477</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.04391767651791056</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.04724991728972761</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.04641354346818938</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.04443096928923529</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.04614117148132579</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.04694570885085114</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.04725456421261698</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.04789022639420715</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.04912067090554295</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.05048004185359178</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.05037572407386426</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.04485749542277584</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.0420544769410538</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.03920419366647288</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.03952717610475487</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.0414011865170516</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.04429770120026499</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0.042467390222517</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.0438830903259253</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.04431079840140084</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.04309084776691496</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.04241594327652254</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.04029363452320367</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.0398886173613251</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.03905726461827874</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0.03895446877773101</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0.03909887764924602</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.03883513738645927</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.03802762459465447</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.03729310711837996</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.03777743240390175</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.03718881749063963</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0.03806269891535186</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0.03745954479974167</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0.03675403582930103</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0.03662486392363706</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.03656622187006864</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>0.03637674369002353</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.03598027869152243</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.03641096808983124</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.03653067207105765</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.03679240177956555</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.03665773571567277</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.03667497455720747</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.0372083763433162</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.03695855870508202</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.03691553137899461</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0.03688163398399302</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0.03679754188179052</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0.0369999835690189</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0.03726742948824202</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0.03722432495742889</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>0.03715198534241648</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>0.03696296615340189</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>0.03681765457623842</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0.03667110425589959</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>0.03580262564334236</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0.035759601650585</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>0.03571662229037753</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>0.03555982866347773</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>0.03531892034247908</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>0.03503078508964341</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>0.03488443744763314</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>0.03494464765469085</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>0.03470780114476524</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>0.0346163662834813</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>0.03448887373191378</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>0.03444586142998274</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>0.03471207501057383</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>0.0347088772628632</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0.03470465220876995</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>0.0347017462306769</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>0.03469881332591962</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0.03469602711545483</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>0.0346941679780679</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0.03469138178011222</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>0.03468893358415714</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>0.03468573750439385</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>0.03468300761359266</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>0.03468083929660315</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>0.03467661435699831</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>0.0345874616270061</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0.03449737591904256</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>0.03440850574776899</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>0.03431961855235355</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>0.0342308732740515</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>0.03414298419131945</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>0.03405425406835749</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>0.03396584088746302</v>
+      </c>
+      <c r="EB3" t="n">
+        <v>0.0338767508620581</v>
+      </c>
+      <c r="EC3" t="n">
+        <v>0.03378809508446867</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>0.03369996072067605</v>
+      </c>
+      <c r="EE3" t="n">
+        <v>0.03360995229100006</v>
+      </c>
+      <c r="EF3" t="n">
+        <v>0.03360676405029039</v>
+      </c>
+      <c r="EG3" t="n">
+        <v>0.03360255154937364</v>
+      </c>
+      <c r="EH3" t="n">
+        <v>0.03359965421236644</v>
+      </c>
+      <c r="EI3" t="n">
+        <v>0.03359673002860242</v>
+      </c>
+      <c r="EJ3" t="n">
+        <v>0.03359395210367433</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>0.03359209849809797</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>0.03358932058561814</v>
+      </c>
+      <c r="EM3" t="n">
+        <v>0.03358687967151752</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>0.03358369309366993</v>
+      </c>
+      <c r="EO3" t="n">
+        <v>0.03358097132114102</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>0.03357880945462854</v>
+      </c>
+      <c r="EQ3" t="n">
+        <v>0.03357459706764265</v>
+      </c>
+      <c r="ER3" t="n">
+        <v>0.03357141211429537</v>
+      </c>
+      <c r="ES3" t="n">
+        <v>0.03368700851001627</v>
+      </c>
+      <c r="ET3" t="n">
+        <v>0.03368411382572378</v>
+      </c>
+      <c r="EU3" t="n">
+        <v>0.03368119231916999</v>
+      </c>
+      <c r="EV3" t="n">
+        <v>0.03367841693793139</v>
+      </c>
+      <c r="EW3" t="n">
+        <v>0.03367656503131511</v>
+      </c>
+      <c r="EX3" t="n">
+        <v>0.03367378966250034</v>
+      </c>
+      <c r="EY3" t="n">
+        <v>0.03367135098427276</v>
+      </c>
+      <c r="EZ3" t="n">
+        <v>0.0336681673230208</v>
+      </c>
+      <c r="FA3" t="n">
+        <v>0.03366544804287708</v>
+      </c>
+      <c r="FB3" t="n">
+        <v>0.0336632881571961</v>
+      </c>
+      <c r="FC3" t="n">
+        <v>0.03365907962149328</v>
+      </c>
+      <c r="FD3" t="n">
+        <v>0.03353879044778996</v>
+      </c>
+      <c r="FE3" t="n">
+        <v>0.03227365365740709</v>
+      </c>
+      <c r="FF3" t="n">
+        <v>0.032444316725595</v>
+      </c>
+      <c r="FG3" t="n">
+        <v>0.03258815692572425</v>
+      </c>
+      <c r="FH3" t="n">
+        <v>0.03287826781028547</v>
+      </c>
+      <c r="FI3" t="n">
+        <v>0.03409303285951837</v>
+      </c>
+      <c r="FJ3" t="n">
+        <v>0.03438356654661323</v>
+      </c>
+      <c r="FK3" t="n">
+        <v>0.03501176100710746</v>
+      </c>
+      <c r="FL3" t="n">
+        <v>0.03489290986573423</v>
+      </c>
+      <c r="FM3" t="n">
+        <v>0.03523991161621631</v>
+      </c>
+      <c r="FN3" t="n">
+        <v>0.03614837440318275</v>
+      </c>
+      <c r="FO3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FP3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FQ3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FR3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FS3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FT3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FU3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FV3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FW3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FX3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FY3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="FZ3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GA3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GB3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GC3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GD3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GE3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GF3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GG3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GH3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GI3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GJ3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+      <c r="GK3" t="n">
+        <v>0.03500000000000036</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>brent</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>82.545</v>
+      </c>
+      <c r="F4" t="n">
+        <v>81.17333333333333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>81.88666666666667</v>
+      </c>
+      <c r="H4" t="n">
+        <v>79.51333333333334</v>
+      </c>
+      <c r="I4" t="n">
+        <v>78.31666666666668</v>
+      </c>
+      <c r="J4" t="n">
+        <v>76.80666666666667</v>
+      </c>
+      <c r="K4" t="n">
+        <v>80.36666666666666</v>
+      </c>
+      <c r="L4" t="n">
+        <v>86.66000000000001</v>
+      </c>
+      <c r="M4" t="n">
+        <v>90.15666666666668</v>
+      </c>
+      <c r="N4" t="n">
+        <v>89.08666666666666</v>
+      </c>
+      <c r="O4" t="n">
+        <v>83.72333333333333</v>
+      </c>
+      <c r="P4" t="n">
+        <v>80.23</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>80.41000000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>83.00333333333334</v>
+      </c>
+      <c r="S4" t="n">
+        <v>86.27666666666666</v>
+      </c>
+      <c r="T4" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="U4" t="n">
+        <v>84.64666666666666</v>
+      </c>
+      <c r="V4" t="n">
+        <v>83.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>82.58666666666666</v>
+      </c>
+      <c r="X4" t="n">
+        <v>79.84333333333332</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>74.66666666666666</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>74.61333333333333</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>75.82666666666665</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>76.19</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>75.81333333333333</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>72.10000000000001</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>68.43666666666667</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>68.00666666666666</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>68.97666666666667</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>70.11666666666667</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>68.96666666666668</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>66.80000000000001</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>65.44333333333333</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>63.62666666666667</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>64.31333333333333</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>66.67666666666666</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>80.20666666666666</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>109.1866666666667</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>103.2766666666667</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>92.10000000000001</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>86.20804900345644</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>85.70239080341851</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>85.09757197462805</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>81.9976910388262</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>80.23327945848136</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>77.99019584865648</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>77.03397637636314</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>76.87813774182122</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>76.90930441943703</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>76.433757798663</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>75.09325513575423</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>74.25741007024706</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>72.67364392630132</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>71.44213868894958</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>70.31406349897634</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>69.23564753950224</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>67.9419548336479</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>66.57146963523638</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>65.75613904261994</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>65.4367542169137</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>65.56710501309625</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>65.69771546962211</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>65.82858610373781</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>65.9597174337202</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>66.09110997887855</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>66.22276425955664</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>66.35468079713472</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>66.48686011403169</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>66.61930273370707</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>66.75200918066317</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>66.88497998044704</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>67.01821565965274</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>67.15171674592318</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>67.28548376795244</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>67.41951725548772</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>67.55381773933146</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>67.68838575134355</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>67.82322182444325</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>67.95832649261149</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>68.09370029089284</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>68.22934375539769</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>68.36525742330439</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>68.50144183286133</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>68.63789752338913</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>68.77462503528271</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>68.91162491001349</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>69.04889769013148</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>69.1864439192675</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>69.32426414213525</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>69.4623589045335</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>69.60072875334828</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>69.73937423655502</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>69.87829590322075</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>70.01749430350617</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>70.156969988668</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>70.29672351106099</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>70.43675542414026</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>70.57706628246336</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>70.71765664169256</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>70.85852705859698</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>70.99967809105489</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>71.14111029805581</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>71.28282423970278</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>71.4248204772146</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>71.56709957292797</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>71.70966209029983</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>71.85250859390953</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>71.99563964946101</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>72.13905582378518</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>72.282757684842</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>72.42674580172287</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>72.57102074465284</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>72.71558308499277</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>72.86043339524178</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>73.00557224903935</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>73.15100022116768</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>73.29671788755392</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>73.44272582527253</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>73.58902461254745</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>73.73561482875448</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>73.88249705442352</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>74.02967187124092</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>74.17713986205173</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>74.32490161086207</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>74.47295770284137</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>74.62130872432475</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>74.76995526281529</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>74.91889790698639</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>75.06813724668415</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>75.21767387292954</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>75.36750837792094</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>75.51764135503639</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>75.66807339883593</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>75.81880510506394</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>75.96983707065158</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>76.12116989371906</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>76.27280417357809</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>76.4247405107342</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>76.57697950688913</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>76.72952176494321</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>76.88236788899781</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>77.03551848435758</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>77.18897415753302</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>77.34273551624277</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>77.4968031694161</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>77.65117772719522</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>77.80585980093775</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>77.96085000321921</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>78.11614894783528</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>78.27175724980442</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>78.42767552537016</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>78.58390439200359</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>78.74044446840587</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>78.84490832467479</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GH4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GI4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GJ4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+      <c r="GK4" t="n">
+        <v>78.89719222435771</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hh</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.653333333333334</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.283333333333333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.206666666666667</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.163333333333334</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.293333333333333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.436666666666667</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.733333333333334</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.776666666666667</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.736666666666666</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.803333333333333</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.473333333333333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.603333333333333</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.736666666666667</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.086666666666666</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.243333333333334</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.113333333333333</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.156666666666667</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.443333333333333</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.086666666666666</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.776666666666667</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4.146666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.553333333333333</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.186666666666667</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3.113333333333333</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.043333333333333</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3.026666666666667</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3.023333333333333</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.316666666666666</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3.746666666666667</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>5.256666666666667</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.793333333333333</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.143333333333333</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.916666666666667</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.953333333333333</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.993333333333334</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.078</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.084666666666667</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.192</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.274666666666667</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.569666666666667</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.985333333333333</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.181</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.898666666666667</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.402666666666667</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.038666666666666</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.991333333333333</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.092</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.221333333333334</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.305</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.346333333333333</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>3.458333333333333</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3.791666666666667</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>4.242</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>4.442666666666667</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.168</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.651</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>3.288</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>3.227666666666666</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>3.334333333333333</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>3.468333333333333</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>3.549</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>3.583333333333333</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>3.667666666666667</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>3.953</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>4.351</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>4.515</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>4.203</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>3.646666666666667</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>3.246666666666667</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>3.167666666666667</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>3.270333333333333</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>3.404333333333333</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>3.494666666666667</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>3.536666666666667</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>3.615333333333334</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>3.893666666666667</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>4.284666666666666</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>4.457999999999999</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>4.176333333333333</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>3.614333333333333</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>3.197333333333333</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>3.083333333333333</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>3.190666666666667</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>3.322666666666667</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>3.400666666666667</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>3.428333333333333</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>3.509666666666666</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>3.779333333333334</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>4.146333333333334</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>4.019333333333333</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>3.483333333333334</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>3.092666666666667</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>2.983</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>3.083333333333333</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>3.214333333333334</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>3.294666666666667</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>3.331999999999999</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>3.729333333333333</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>4.112</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>4.258666666666667</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>3.969666666666667</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>3.418000000000001</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>3.010666666666667</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>2.887666666666667</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>2.978666666666667</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>3.099</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>3.167666666666667</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>3.196666666666667</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>3.281</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>3.542666666666667</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>3.878333333333333</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>3.990333333333334</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>3.707333333333333</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>3.206</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>2.849666666666666</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>2.767333333333333</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>2.872333333333334</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>3.007333333333333</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>3.086333333333334</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>3.126333333333334</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>3.223</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>3.471333333333334</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>3.923</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>3.711333333333334</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>3.266333333333333</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>2.919666666666667</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>2.826333333333333</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>2.933</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>3.148</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>3.188333333333333</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>3.288666666666666</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>3.517333333333333</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>3.805666666666667</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>3.934</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>3.785666666666667</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>3.432333333333334</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>3.151666666666667</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>3.043666666666667</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>3.081999999999999</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>3.113666666666667</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>3.147333333333334</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>3.234333333333333</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>3.419666666666667</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>3.679666666666667</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>3.873</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GH5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GI5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GJ5" t="n">
+        <v>3.963</v>
+      </c>
+      <c r="GK5" t="n">
+        <v>3.963</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dolar</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.200681818181819</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.186185353535354</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.194610525545309</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.134294363929146</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.071343522178304</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.951378787878788</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.878412121212122</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.851981159420291</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.880455603864735</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.968458778467909</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.966724285714286</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.953475952380953</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.90332681818182</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.925343309409889</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4.952973309409889</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.024539976076555</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.080759357864358</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5.217039357864358</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.354690148378192</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5.49454548748353</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.545409376372419</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.572762999560825</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5.657577752351894</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.842731720605862</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>5.975286397812713</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.9614820995671</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.844742751196172</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>5.763858191311613</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>5.731105096073517</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5.664519920634921</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5.580977339544513</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.507490037957211</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>5.447608068260242</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>5.399952995796474</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>5.36459593648152</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5.393156542542125</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>5.377322450064555</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>5.330577128427127</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5.25674227994228</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5.155092676767677</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.113947826086956</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.048115476190477</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.083757142857142</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5.155857142857143</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.196666666666666</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.283333333333333</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5.350000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.313333333333333</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.293333333333333</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.286666666666666</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.283333333333334</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.276666666666666</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.273333333333333</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>5.263333333333333</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>5.256666666666667</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>5.253333333333333</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>5.253333333333333</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>5.256666666666667</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>5.263333333333333</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>5.273333333333333</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>5.276666666666667</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>5.283333333333334</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>5.286666666666666</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>5.293333333333333</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>5.296666666666667</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>5.303333333333334</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>5.306666666666666</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>5.313333333333333</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>5.316666666666666</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>5.323333333333333</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>5.326666666666667</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>5.336666666666666</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>5.343333333333334</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>5.346666666666667</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>5.349999999999999</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>5.356666666666666</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>5.363333333333333</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>5.366666666666667</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>5.373333333333334</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>5.376666666666666</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>5.383333333333333</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>5.386666666666667</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>5.393333333333334</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>5.396666666666666</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>5.400000000000001</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>5.403333333333333</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>5.406666666666666</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>5.413333333333334</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>5.416666666666667</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>5.419999999999999</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>5.423333333333333</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>5.426666666666667</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>5.433333333333334</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>5.436666666666667</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>5.443333333333334</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>5.446666666666666</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>5.453333333333333</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>5.456666666666667</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>5.463333333333334</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>5.466666666666666</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>5.473333333333334</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>5.476666666666667</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>5.483333333333334</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>5.486666666666667</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>5.489999999999999</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>5.493333333333333</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>5.496666666666667</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>5.503333333333333</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>5.506666666666667</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>5.510000000000001</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>5.513333333333333</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>5.516666666666666</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>5.523333333333333</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>5.526666666666667</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>5.533333333333334</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>5.536666666666666</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>5.543333333333333</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>5.546666666666667</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>5.553333333333334</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>5.556666666666666</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>5.563333333333333</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>5.566666666666666</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>5.573333333333333</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>5.577001466666666</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>5.581004460264</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>5.582009041066848</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>5.58301380269424</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>5.584018745178725</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>5.585023868552859</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>5.586029172849199</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>5.587034658100312</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>5.588040324338771</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>5.589046171597151</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>5.59005219990804</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>5.591058409304023</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>5.592064799817699</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>5.593071371481667</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>5.594078124328534</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>5.595085058390914</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>5.596092173701424</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>5.597099470292691</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>5.598106948197344</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>5.59911460744802</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>5.600122448077361</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>5.601130470118015</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>5.602138673602636</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>5.603147058563885</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>5.604155625034427</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>5.605164373046933</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>5.606173302634083</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>5.607182413828557</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>5.608191706663047</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>5.609201181170246</v>
+      </c>
+      <c r="GH6" t="n">
+        <v>5.610210837382858</v>
+      </c>
+      <c r="GI6" t="n">
+        <v>5.611220675333587</v>
+      </c>
+      <c r="GJ6" t="n">
+        <v>5.612230695055147</v>
+      </c>
+      <c r="GK6" t="n">
+        <v>5.613240896580257</v>
       </c>
     </row>
   </sheetData>
@@ -29162,13 +39014,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{255C8C55-9EC0-47A8-86C4-3F2F5A3AE090}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34288D85-C9A7-402A-B541-D88D6392162A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBD2EBC1-96C7-48CB-B8B3-00A4540EB9BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0830A4D-F51D-4F41-A47D-448CE55BE0CA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A714EE7B-7021-44EF-8CCC-DB37B2A4EE1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29111C9F-2197-4F6D-A16C-7E360DF92CB1}"/>
 </file>
--- a/empresas/gnlink/analises-financeiras/bp/gnlink-bp-historico.xlsx
+++ b/empresas/gnlink/analises-financeiras/bp/gnlink-bp-historico.xlsx
@@ -29,12 +29,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpexRegasCli" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpexRegasGlob" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpexRegasSeed" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PremLiquef" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MolPremCfg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MolPisoTeto" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesOpex" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustoTotal" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRE" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OpexCompTerm" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PremLiquef" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MolPremCfg" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MolPisoTeto" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesOpex" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustoTotal" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRE" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46438,433 +46439,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>planta</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>comp_tarifa</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>comp_ini_ord</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>comp_fim_ord</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>p4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>p5</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>p6</t>
+          <t>term_tarifa</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>agua_rate</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10000</v>
+        <v>24318</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>gerador</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>86000</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>24318</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>glycol_rate</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>24331</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>24367</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mercaptano_g1</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="C5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mercaptano_g2</t>
-        </is>
-      </c>
       <c r="B6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C6" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mercaptano_rate</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>52000</v>
-      </c>
-      <c r="C7" t="n">
-        <v>52000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>oem</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>334084</v>
-      </c>
-      <c r="D8" t="n">
-        <v>307254</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>oleo_rate</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>29000</v>
-      </c>
-      <c r="C9" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D9" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>outros_rate</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C10" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D10" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>perdaFrac</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>precoMWh</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>390</v>
-      </c>
-      <c r="C12" t="n">
-        <v>426.0166752712964</v>
-      </c>
-      <c r="D12" t="n">
-        <v>565.4200368657117</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>propano_g1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>propano_g2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" t="n">
-        <v>12</v>
-      </c>
-      <c r="E14" t="n">
-        <v>12</v>
-      </c>
-      <c r="F14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G14" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>propano_rate</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>49572</v>
-      </c>
-      <c r="C15" t="n">
-        <v>65000</v>
-      </c>
-      <c r="D15" t="n">
-        <v>55000</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>purga_c</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>purga_start</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>residuos_rate</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D18" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -46879,7 +46558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46922,178 +46601,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>custoBase</t>
+          <t>agua_rate</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.93</v>
+        <v>4000</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0949</v>
+        <v>1500</v>
       </c>
       <c r="D2" t="n">
-        <v>1.619937813846938</v>
+        <v>10000</v>
       </c>
       <c r="E2" t="n">
-        <v>1.612542156903223</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.819929131227396</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2.244374262149979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>indicador</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IPCA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Brent</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Brent</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Brent</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dólar</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>IPCA + Brent</t>
-        </is>
+          <t>gerador</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>86000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dataBaseOrd</t>
+          <t>glycol_rate</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24334</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>24304</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>24298</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>24314</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>24317</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>24317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ocorrencia</t>
+          <t>mercaptano_g1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>refDateOrd</t>
+          <t>mercaptano_g2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24334</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>24316</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>24316</v>
-      </c>
-      <c r="E6" t="n">
-        <v>24317</v>
-      </c>
-      <c r="F6" t="n">
-        <v>24317</v>
-      </c>
-      <c r="G6" t="n">
-        <v>24317</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dolarBaseAR</t>
+          <t>mercaptano_rate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.127571428571429</v>
+        <v>52000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>52000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fixaSAL</t>
+          <t>oem</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.13</v>
+        <v>300000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>334084</v>
+      </c>
+      <c r="D8" t="n">
+        <v>307254</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pctBrentSAL</t>
+          <t>oleo_rate</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06</v>
+        <v>29000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>divisorSAL</t>
+          <t>outros_rate</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26.8081</v>
+        <v>5000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perdaFrac</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>precoMWh</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>390</v>
+      </c>
+      <c r="C12" t="n">
+        <v>426.0166752712964</v>
+      </c>
+      <c r="D12" t="n">
+        <v>565.4200368657117</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>propano_g1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>propano_g2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>propano_rate</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>49572</v>
+      </c>
+      <c r="C15" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>purga_c</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>purga_start</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>residuos_rate</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -47107,2786 +46999,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GK13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>kind_planta</t>
+          <t>key</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2023-07</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>2027-04</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>2027-05</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>2027-06</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>2027-07</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>2027-08</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>2027-09</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>2027-10</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>2027-11</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>2027-12</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>2028-01</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>2028-02</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>2028-03</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>2028-04</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>2028-05</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>2028-06</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>2028-07</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>2028-08</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>2028-09</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>2028-10</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>2028-11</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>2028-12</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>2029-01</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>2029-02</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>2029-03</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>2029-04</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>2029-05</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>2029-06</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>2029-07</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>2029-08</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>2029-09</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>2029-10</t>
-        </is>
-      </c>
-      <c r="CF1" t="inlineStr">
-        <is>
-          <t>2029-11</t>
-        </is>
-      </c>
-      <c r="CG1" t="inlineStr">
-        <is>
-          <t>2029-12</t>
-        </is>
-      </c>
-      <c r="CH1" t="inlineStr">
-        <is>
-          <t>2030-01</t>
-        </is>
-      </c>
-      <c r="CI1" t="inlineStr">
-        <is>
-          <t>2030-02</t>
-        </is>
-      </c>
-      <c r="CJ1" t="inlineStr">
-        <is>
-          <t>2030-03</t>
-        </is>
-      </c>
-      <c r="CK1" t="inlineStr">
-        <is>
-          <t>2030-04</t>
-        </is>
-      </c>
-      <c r="CL1" t="inlineStr">
-        <is>
-          <t>2030-05</t>
-        </is>
-      </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>2030-06</t>
-        </is>
-      </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>2030-07</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>2030-08</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>2030-09</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>2030-10</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>2030-11</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>2030-12</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>2031-01</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>2031-02</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>2031-03</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>2031-04</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>2031-05</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>2031-06</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>2031-07</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>2031-08</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>2031-09</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>2031-10</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>2031-11</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>2031-12</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>2032-01</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>2032-02</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>2032-03</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>2032-04</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>2032-05</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>2032-06</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>2032-07</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>2032-08</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>2032-09</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>2032-10</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>2032-11</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>2032-12</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>2033-01</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>2033-02</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>2033-03</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>2033-04</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>2033-05</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>2033-06</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>2033-07</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>2033-08</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>2033-09</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>2033-10</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>2033-11</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>2033-12</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>2034-01</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>2034-02</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>2034-03</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>2034-04</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>2034-05</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>2034-06</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>2034-07</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>2034-08</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>2034-09</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>2034-10</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>2034-11</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>2034-12</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>2035-01</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>2035-02</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>2035-03</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>2035-04</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>2035-05</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>2035-06</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>2035-07</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>2035-08</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>2035-09</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>2035-10</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>2035-11</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>2035-12</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>2036-01</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
-        <is>
-          <t>2036-02</t>
-        </is>
-      </c>
-      <c r="FD1" t="inlineStr">
-        <is>
-          <t>2036-03</t>
-        </is>
-      </c>
-      <c r="FE1" t="inlineStr">
-        <is>
-          <t>2036-04</t>
-        </is>
-      </c>
-      <c r="FF1" t="inlineStr">
-        <is>
-          <t>2036-05</t>
-        </is>
-      </c>
-      <c r="FG1" t="inlineStr">
-        <is>
-          <t>2036-06</t>
-        </is>
-      </c>
-      <c r="FH1" t="inlineStr">
-        <is>
-          <t>2036-07</t>
-        </is>
-      </c>
-      <c r="FI1" t="inlineStr">
-        <is>
-          <t>2036-08</t>
-        </is>
-      </c>
-      <c r="FJ1" t="inlineStr">
-        <is>
-          <t>2036-09</t>
-        </is>
-      </c>
-      <c r="FK1" t="inlineStr">
-        <is>
-          <t>2036-10</t>
-        </is>
-      </c>
-      <c r="FL1" t="inlineStr">
-        <is>
-          <t>2036-11</t>
-        </is>
-      </c>
-      <c r="FM1" t="inlineStr">
-        <is>
-          <t>2036-12</t>
-        </is>
-      </c>
-      <c r="FN1" t="inlineStr">
-        <is>
-          <t>2037-01</t>
-        </is>
-      </c>
-      <c r="FO1" t="inlineStr">
-        <is>
-          <t>2037-02</t>
-        </is>
-      </c>
-      <c r="FP1" t="inlineStr">
-        <is>
-          <t>2037-03</t>
-        </is>
-      </c>
-      <c r="FQ1" t="inlineStr">
-        <is>
-          <t>2037-04</t>
-        </is>
-      </c>
-      <c r="FR1" t="inlineStr">
-        <is>
-          <t>2037-05</t>
-        </is>
-      </c>
-      <c r="FS1" t="inlineStr">
-        <is>
-          <t>2037-06</t>
-        </is>
-      </c>
-      <c r="FT1" t="inlineStr">
-        <is>
-          <t>2037-07</t>
-        </is>
-      </c>
-      <c r="FU1" t="inlineStr">
-        <is>
-          <t>2037-08</t>
-        </is>
-      </c>
-      <c r="FV1" t="inlineStr">
-        <is>
-          <t>2037-09</t>
-        </is>
-      </c>
-      <c r="FW1" t="inlineStr">
-        <is>
-          <t>2037-10</t>
-        </is>
-      </c>
-      <c r="FX1" t="inlineStr">
-        <is>
-          <t>2037-11</t>
-        </is>
-      </c>
-      <c r="FY1" t="inlineStr">
-        <is>
-          <t>2037-12</t>
-        </is>
-      </c>
-      <c r="FZ1" t="inlineStr">
-        <is>
-          <t>2038-01</t>
-        </is>
-      </c>
-      <c r="GA1" t="inlineStr">
-        <is>
-          <t>2038-02</t>
-        </is>
-      </c>
-      <c r="GB1" t="inlineStr">
-        <is>
-          <t>2038-03</t>
-        </is>
-      </c>
-      <c r="GC1" t="inlineStr">
-        <is>
-          <t>2038-04</t>
-        </is>
-      </c>
-      <c r="GD1" t="inlineStr">
-        <is>
-          <t>2038-05</t>
-        </is>
-      </c>
-      <c r="GE1" t="inlineStr">
-        <is>
-          <t>2038-06</t>
-        </is>
-      </c>
-      <c r="GF1" t="inlineStr">
-        <is>
-          <t>2038-07</t>
-        </is>
-      </c>
-      <c r="GG1" t="inlineStr">
-        <is>
-          <t>2038-08</t>
-        </is>
-      </c>
-      <c r="GH1" t="inlineStr">
-        <is>
-          <t>2038-09</t>
-        </is>
-      </c>
-      <c r="GI1" t="inlineStr">
-        <is>
-          <t>2038-10</t>
-        </is>
-      </c>
-      <c r="GJ1" t="inlineStr">
-        <is>
-          <t>2038-11</t>
-        </is>
-      </c>
-      <c r="GK1" t="inlineStr">
-        <is>
-          <t>2038-12</t>
+          <t>p6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>piso_1</t>
-        </is>
+          <t>custoBase</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0949</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.619937813846938</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.612542156903223</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.819929131227396</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.244374262149979</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>piso_2</t>
+          <t>indicador</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IPCA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dólar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>IPCA + Brent</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>piso_3</t>
+          <t>dataBaseOrd</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>24334</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>24304</v>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>24298</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>24314</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>24317</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
-      </c>
-      <c r="H4" t="n">
-        <v>70</v>
-      </c>
-      <c r="I4" t="n">
-        <v>70</v>
-      </c>
-      <c r="J4" t="n">
-        <v>70</v>
-      </c>
-      <c r="K4" t="n">
-        <v>70</v>
-      </c>
-      <c r="L4" t="n">
-        <v>70</v>
-      </c>
-      <c r="M4" t="n">
-        <v>70</v>
-      </c>
-      <c r="N4" t="n">
-        <v>70</v>
-      </c>
-      <c r="O4" t="n">
-        <v>70</v>
-      </c>
-      <c r="P4" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>70</v>
-      </c>
-      <c r="R4" t="n">
-        <v>70</v>
-      </c>
-      <c r="S4" t="n">
-        <v>70</v>
-      </c>
-      <c r="T4" t="n">
-        <v>70</v>
-      </c>
-      <c r="U4" t="n">
-        <v>70</v>
-      </c>
-      <c r="V4" t="n">
-        <v>70</v>
-      </c>
-      <c r="W4" t="n">
-        <v>70</v>
-      </c>
-      <c r="X4" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>70</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>72.06499034843883</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>74.88937847867476</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>76.72265114650324</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>78.60080185635692</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>80.52492921112852</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="CW4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>82.49615870722619</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>84.51564339291983</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DT4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DX4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DY4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="EA4" t="n">
-        <v>86.58456454280358</v>
-      </c>
-      <c r="EB4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EC4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="ED4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EE4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EF4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EG4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EH4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EI4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EJ4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EK4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EL4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EM4" t="n">
-        <v>88.70413234876892</v>
-      </c>
-      <c r="EN4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="EO4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="EP4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="EQ4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="ER4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="ES4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="ET4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="EU4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="EV4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="EW4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="EX4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="EY4" t="n">
-        <v>90.8755866278927</v>
-      </c>
-      <c r="EZ4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FA4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FB4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FC4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FD4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FE4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FF4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FG4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FH4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FI4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FJ4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FK4" t="n">
-        <v>93.10019754765399</v>
-      </c>
-      <c r="FL4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FM4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FN4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FO4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FP4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FQ4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FR4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FS4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FT4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FU4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FV4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FW4" t="n">
-        <v>94.99688713904291</v>
-      </c>
-      <c r="FX4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="FY4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="FZ4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GA4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GB4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GC4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GD4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GE4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GF4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GG4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GH4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GI4" t="n">
-        <v>96.89682488182379</v>
-      </c>
-      <c r="GJ4" t="n">
-        <v>98.83476137946029</v>
-      </c>
-      <c r="GK4" t="n">
-        <v>98.83476137946029</v>
+        <v>24317</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>piso_4</t>
-        </is>
+          <t>ocorrencia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>piso_5</t>
-        </is>
+          <t>refDateOrd</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>24334</v>
+      </c>
+      <c r="C6" t="n">
+        <v>24316</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24316</v>
+      </c>
+      <c r="E6" t="n">
+        <v>24317</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24317</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24317</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>piso_6</t>
+          <t>dolarBaseAR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="C7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="D7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="E7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="F7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="G7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="H7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="I7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="J7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="K7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="L7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="M7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="N7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="O7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="P7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="R7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="S7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="T7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="U7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="V7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="W7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="X7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>97.10333333333334</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>99.24549265195901</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>101.6749967122153</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>104.1639744051886</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>106.7138816300669</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>109.3262099260748</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>112.0024873449323</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="ED7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="EE7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="EF7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="EG7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="EH7" t="n">
-        <v>114.7442793446715</v>
-      </c>
-      <c r="EI7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="EJ7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="EK7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="EL7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="EM7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="EN7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="EO7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="EP7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="EQ7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="ER7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="ES7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="ET7" t="n">
-        <v>117.5531897053331</v>
-      </c>
-      <c r="EU7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="EV7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="EW7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="EX7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="EY7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="EZ7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="FA7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="FB7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="FC7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="FD7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="FE7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="FF7" t="n">
-        <v>120.4308614670799</v>
-      </c>
-      <c r="FG7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FH7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FI7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FJ7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FK7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FL7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FM7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FN7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FO7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FP7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FQ7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FR7" t="n">
-        <v>123.1089327638793</v>
-      </c>
-      <c r="FS7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="FT7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="FU7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="FV7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="FW7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="FX7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="FY7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="FZ7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="GA7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="GB7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="GC7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="GD7" t="n">
-        <v>125.5711114191569</v>
-      </c>
-      <c r="GE7" t="n">
-        <v>128.0825336475401</v>
-      </c>
-      <c r="GF7" t="n">
-        <v>128.0825336475401</v>
-      </c>
-      <c r="GG7" t="n">
-        <v>128.0825336475401</v>
-      </c>
-      <c r="GH7" t="n">
-        <v>128.0825336475401</v>
-      </c>
-      <c r="GI7" t="n">
-        <v>128.0825336475401</v>
-      </c>
-      <c r="GJ7" t="n">
-        <v>128.0825336475401</v>
-      </c>
-      <c r="GK7" t="n">
-        <v>128.0825336475401</v>
+        <v>5.127571428571429</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>teto_1</t>
-        </is>
+          <t>fixaSAL</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>teto_2</t>
-        </is>
+          <t>pctBrentSAL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>teto_3</t>
+          <t>divisorSAL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
-      </c>
-      <c r="C10" t="n">
-        <v>120</v>
-      </c>
-      <c r="D10" t="n">
-        <v>120</v>
-      </c>
-      <c r="E10" t="n">
-        <v>120</v>
-      </c>
-      <c r="F10" t="n">
-        <v>120</v>
-      </c>
-      <c r="G10" t="n">
-        <v>120</v>
-      </c>
-      <c r="H10" t="n">
-        <v>120</v>
-      </c>
-      <c r="I10" t="n">
-        <v>120</v>
-      </c>
-      <c r="J10" t="n">
-        <v>120</v>
-      </c>
-      <c r="K10" t="n">
-        <v>120</v>
-      </c>
-      <c r="L10" t="n">
-        <v>120</v>
-      </c>
-      <c r="M10" t="n">
-        <v>120</v>
-      </c>
-      <c r="N10" t="n">
-        <v>120</v>
-      </c>
-      <c r="O10" t="n">
-        <v>120</v>
-      </c>
-      <c r="P10" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>120</v>
-      </c>
-      <c r="R10" t="n">
-        <v>120</v>
-      </c>
-      <c r="S10" t="n">
-        <v>120</v>
-      </c>
-      <c r="T10" t="n">
-        <v>120</v>
-      </c>
-      <c r="U10" t="n">
-        <v>120</v>
-      </c>
-      <c r="V10" t="n">
-        <v>120</v>
-      </c>
-      <c r="W10" t="n">
-        <v>120</v>
-      </c>
-      <c r="X10" t="n">
-        <v>120</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>120</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>123.5399834544666</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>128.3817916777282</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>131.524544822577</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>134.7442317537547</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>138.042735790506</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>141.4219863552449</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>144.8839601021483</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DY10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="EA10" t="n">
-        <v>148.4306820733776</v>
-      </c>
-      <c r="EB10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EC10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="ED10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EE10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EF10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EG10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EH10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EI10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EJ10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EK10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EL10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EM10" t="n">
-        <v>152.0642268836039</v>
-      </c>
-      <c r="EN10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="EO10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="EP10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="EQ10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="ER10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="ES10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="ET10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="EU10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="EV10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="EW10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="EX10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="EY10" t="n">
-        <v>155.7867199335304</v>
-      </c>
-      <c r="EZ10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FA10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FB10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FC10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FD10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FE10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FF10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FG10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FH10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FI10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FJ10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FK10" t="n">
-        <v>159.6003386531212</v>
-      </c>
-      <c r="FL10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FM10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FN10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FO10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FP10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FQ10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FR10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FS10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FT10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FU10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FV10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FW10" t="n">
-        <v>162.8518065240736</v>
-      </c>
-      <c r="FX10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="FY10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="FZ10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GA10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GB10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GC10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GD10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GE10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GF10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GG10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GH10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GI10" t="n">
-        <v>166.1088426545551</v>
-      </c>
-      <c r="GJ10" t="n">
-        <v>169.4310195076463</v>
-      </c>
-      <c r="GK10" t="n">
-        <v>169.4310195076463</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>teto_4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>teto_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>teto_6</t>
-        </is>
+        <v>26.8081</v>
       </c>
     </row>
   </sheetData>
@@ -49900,13 +47227,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GK3"/>
+  <dimension ref="A1:GK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>kind_planta</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -50873,993 +48200,1813 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corr556</t>
-        </is>
-      </c>
-      <c r="AL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.038538936489141</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1.078293190578425</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>1.116881572576544</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>1.1575252573916</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>1.197439841740066</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1.238342960911352</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1.280084757705804</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>1.322442923647435</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>1.366311279749215</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FM2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FN2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FP2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FQ2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FR2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FS2" t="n">
-        <v>1.410572645063492</v>
-      </c>
-      <c r="FT2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="FU2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="FV2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="FW2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="FX2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="FY2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="FZ2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="GA2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="GB2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="GC2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="GD2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="GE2" t="n">
-        <v>1.45916797946202</v>
-      </c>
-      <c r="GF2" t="n">
-        <v>1.509437461259882</v>
-      </c>
-      <c r="GG2" t="n">
-        <v>1.509437461259882</v>
-      </c>
-      <c r="GH2" t="n">
-        <v>1.509437461259882</v>
-      </c>
-      <c r="GI2" t="n">
-        <v>1.509437461259882</v>
-      </c>
-      <c r="GJ2" t="n">
-        <v>1.509437461259882</v>
-      </c>
-      <c r="GK2" t="n">
-        <v>1.509437461259882</v>
+          <t>piso_1</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vol192</t>
-        </is>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>184.533333333333</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>207.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>201</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>755.7</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>3240.776451612901</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2616.15033333333</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1592.16166666667</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1186.66935483871</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1230.71666666667</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>815.217741935484</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1234.30967741935</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>644.875</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1002.12903225806</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1599.25</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1076.75935483871</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>708.6333333333333</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1263.734193548387</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1824.58064516129</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6800</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8000</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8000</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8464.516129032258</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>13300</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>15398</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>15398</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>15398</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DD3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DE3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DF3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DH3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DP3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DQ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DR3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DS3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DX3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DY3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EA3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EB3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EC3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="ED3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EE3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EF3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EG3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EH3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EI3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EJ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EK3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EL3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EM3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EN3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EO3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EP3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EQ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="ER3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="ES3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="ET3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EU3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EV3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EW3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EX3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EY3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="EZ3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="FA3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="FB3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="FC3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="FD3" t="n">
-        <v>17496</v>
-      </c>
-      <c r="FE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="FZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="GK3" t="n">
-        <v>0</v>
+          <t>piso_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>piso_3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="n">
+        <v>70</v>
+      </c>
+      <c r="D4" t="n">
+        <v>70</v>
+      </c>
+      <c r="E4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70</v>
+      </c>
+      <c r="G4" t="n">
+        <v>70</v>
+      </c>
+      <c r="H4" t="n">
+        <v>70</v>
+      </c>
+      <c r="I4" t="n">
+        <v>70</v>
+      </c>
+      <c r="J4" t="n">
+        <v>70</v>
+      </c>
+      <c r="K4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L4" t="n">
+        <v>70</v>
+      </c>
+      <c r="M4" t="n">
+        <v>70</v>
+      </c>
+      <c r="N4" t="n">
+        <v>70</v>
+      </c>
+      <c r="O4" t="n">
+        <v>70</v>
+      </c>
+      <c r="P4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>70</v>
+      </c>
+      <c r="R4" t="n">
+        <v>70</v>
+      </c>
+      <c r="S4" t="n">
+        <v>70</v>
+      </c>
+      <c r="T4" t="n">
+        <v>70</v>
+      </c>
+      <c r="U4" t="n">
+        <v>70</v>
+      </c>
+      <c r="V4" t="n">
+        <v>70</v>
+      </c>
+      <c r="W4" t="n">
+        <v>70</v>
+      </c>
+      <c r="X4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>72.06499034843883</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>74.88937847867476</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>76.72265114650324</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>78.60080185635692</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>80.52492921112852</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>82.49615870722619</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>84.51564339291983</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>86.58456454280358</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>88.70413234876892</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>90.8755866278927</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>93.10019754765399</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>94.99688713904291</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GH4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GI4" t="n">
+        <v>96.89682488182379</v>
+      </c>
+      <c r="GJ4" t="n">
+        <v>98.83476137946029</v>
+      </c>
+      <c r="GK4" t="n">
+        <v>98.83476137946029</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>piso_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>piso_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>piso_6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="C7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="D7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="E7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="F7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="H7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="I7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="J7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="K7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="L7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="M7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="N7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="O7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="P7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="R7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="S7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="T7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="U7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="W7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="X7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>97.10333333333334</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>99.24549265195901</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>101.6749967122153</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>104.1639744051886</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>106.7138816300669</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>109.3262099260748</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>112.0024873449323</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>114.7442793446715</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>117.5531897053331</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>120.4308614670799</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>123.1089327638793</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>125.5711114191569</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>128.0825336475401</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>128.0825336475401</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>128.0825336475401</v>
+      </c>
+      <c r="GH7" t="n">
+        <v>128.0825336475401</v>
+      </c>
+      <c r="GI7" t="n">
+        <v>128.0825336475401</v>
+      </c>
+      <c r="GJ7" t="n">
+        <v>128.0825336475401</v>
+      </c>
+      <c r="GK7" t="n">
+        <v>128.0825336475401</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>teto_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>teto_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>teto_3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>120</v>
+      </c>
+      <c r="C10" t="n">
+        <v>120</v>
+      </c>
+      <c r="D10" t="n">
+        <v>120</v>
+      </c>
+      <c r="E10" t="n">
+        <v>120</v>
+      </c>
+      <c r="F10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G10" t="n">
+        <v>120</v>
+      </c>
+      <c r="H10" t="n">
+        <v>120</v>
+      </c>
+      <c r="I10" t="n">
+        <v>120</v>
+      </c>
+      <c r="J10" t="n">
+        <v>120</v>
+      </c>
+      <c r="K10" t="n">
+        <v>120</v>
+      </c>
+      <c r="L10" t="n">
+        <v>120</v>
+      </c>
+      <c r="M10" t="n">
+        <v>120</v>
+      </c>
+      <c r="N10" t="n">
+        <v>120</v>
+      </c>
+      <c r="O10" t="n">
+        <v>120</v>
+      </c>
+      <c r="P10" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>120</v>
+      </c>
+      <c r="R10" t="n">
+        <v>120</v>
+      </c>
+      <c r="S10" t="n">
+        <v>120</v>
+      </c>
+      <c r="T10" t="n">
+        <v>120</v>
+      </c>
+      <c r="U10" t="n">
+        <v>120</v>
+      </c>
+      <c r="V10" t="n">
+        <v>120</v>
+      </c>
+      <c r="W10" t="n">
+        <v>120</v>
+      </c>
+      <c r="X10" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>120</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>123.5399834544666</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>128.3817916777282</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>131.524544822577</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>134.7442317537547</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>138.042735790506</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>141.4219863552449</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>144.8839601021483</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>148.4306820733776</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>152.0642268836039</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>155.7867199335304</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>159.6003386531212</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>162.8518065240736</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GH10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GI10" t="n">
+        <v>166.1088426545551</v>
+      </c>
+      <c r="GJ10" t="n">
+        <v>169.4310195076463</v>
+      </c>
+      <c r="GK10" t="n">
+        <v>169.4310195076463</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>teto_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>teto_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>teto_6</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -51873,13 +50020,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GK2"/>
+  <dimension ref="A1:GK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>linha</t>
+          <t>key</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -52846,137 +50993,993 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>custo_total</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>101115.17</v>
-      </c>
-      <c r="V2" t="n">
-        <v>131267.68</v>
-      </c>
-      <c r="W2" t="n">
-        <v>368593.3848637836</v>
-      </c>
-      <c r="X2" t="n">
-        <v>121111.8842068603</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>713169.4339314839</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1539854.56</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1262838.71</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1209587.05</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1189484.152830585</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1135054.626607902</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1977744.526315656</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2411333.168016748</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2271077.361507017</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2361676.657432924</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2476849.703709069</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2671730.809172639</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1929954.284674397</v>
+          <t>corr556</t>
+        </is>
       </c>
       <c r="AL2" t="n">
-        <v>5598597.617913179</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>3175108.746426018</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>5308355.458171361</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>5761089.073076983</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>6238587.512104752</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7093367.230697965</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>7596452.167459536</v>
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.038538936489141</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1.078293190578425</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>1.116881572576544</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1.1575252573916</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1.197439841740066</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1.238342960911352</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1.280084757705804</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>1.322442923647435</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>1.366311279749215</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>1.410572645063492</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>1.45916797946202</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>1.509437461259882</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>1.509437461259882</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>1.509437461259882</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>1.509437461259882</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>1.509437461259882</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>1.509437461259882</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>vol192</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>184.533333333333</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>201</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>755.7</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3240.776451612901</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2616.15033333333</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1592.16166666667</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1186.66935483871</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1230.71666666667</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>815.217741935484</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1234.30967741935</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>644.875</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1002.12903225806</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1599.25</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1076.75935483871</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>708.6333333333333</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1263.734193548387</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1824.58064516129</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6800</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8464.516129032258</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>13300</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>15398</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>15398</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>15398</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EB3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EC3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="ED3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EE3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EF3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EG3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EH3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EI3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EJ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EM3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EO3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EQ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="ER3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="ES3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="ET3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EU3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EV3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EW3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EX3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EY3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="EZ3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="FA3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="FB3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="FC3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="FD3" t="n">
+        <v>17496</v>
+      </c>
+      <c r="FE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -52985,6 +51988,1123 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:GK2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>linha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>2027-04</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>2027-05</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>2027-06</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>2027-07</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>2027-08</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>2027-09</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>2027-11</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>2028-01</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>2028-02</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>2028-04</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>2028-06</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>2028-08</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>2028-09</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>2028-10</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>2028-11</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>2028-12</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>2029-01</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>2029-02</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>2029-03</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>2029-04</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>2029-05</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>2029-06</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>2029-07</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>2029-08</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>2029-09</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>2029-10</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>2029-11</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>2029-12</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>2030-01</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>2030-02</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>2030-03</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>2030-04</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>2030-05</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>2030-06</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>2030-07</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>2030-08</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>2030-09</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>2030-10</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>2030-11</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>2030-12</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>2031-01</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>2031-02</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>2031-03</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>2031-04</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>2031-05</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>2031-06</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>2031-07</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>2031-08</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>2031-09</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>2031-10</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>2031-11</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>2031-12</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>2032-01</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>2032-02</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>2032-03</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>2032-04</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>2032-05</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>2032-06</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>2032-07</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>2032-08</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>2032-09</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>2032-10</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>2032-11</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>2032-12</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>2033-01</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>2033-02</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>2033-03</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>2033-04</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>2033-05</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>2033-06</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>2033-07</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>2033-08</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>2033-09</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>2033-10</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>2033-11</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>2033-12</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>2034-01</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>2034-02</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>2034-03</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>2034-04</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>2034-05</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>2034-06</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>2034-07</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>2034-08</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>2034-09</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>2034-10</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>2034-11</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>2035-01</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>2035-02</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>2035-03</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>2035-04</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>2035-05</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>2035-06</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>2035-07</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>2035-08</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>2035-09</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>2035-10</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>2035-11</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>2035-12</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>2036-01</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>2036-02</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>2036-03</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
+        <is>
+          <t>2036-04</t>
+        </is>
+      </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t>2036-05</t>
+        </is>
+      </c>
+      <c r="FG1" t="inlineStr">
+        <is>
+          <t>2036-06</t>
+        </is>
+      </c>
+      <c r="FH1" t="inlineStr">
+        <is>
+          <t>2036-07</t>
+        </is>
+      </c>
+      <c r="FI1" t="inlineStr">
+        <is>
+          <t>2036-08</t>
+        </is>
+      </c>
+      <c r="FJ1" t="inlineStr">
+        <is>
+          <t>2036-09</t>
+        </is>
+      </c>
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>2036-10</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
+        <is>
+          <t>2036-11</t>
+        </is>
+      </c>
+      <c r="FM1" t="inlineStr">
+        <is>
+          <t>2036-12</t>
+        </is>
+      </c>
+      <c r="FN1" t="inlineStr">
+        <is>
+          <t>2037-01</t>
+        </is>
+      </c>
+      <c r="FO1" t="inlineStr">
+        <is>
+          <t>2037-02</t>
+        </is>
+      </c>
+      <c r="FP1" t="inlineStr">
+        <is>
+          <t>2037-03</t>
+        </is>
+      </c>
+      <c r="FQ1" t="inlineStr">
+        <is>
+          <t>2037-04</t>
+        </is>
+      </c>
+      <c r="FR1" t="inlineStr">
+        <is>
+          <t>2037-05</t>
+        </is>
+      </c>
+      <c r="FS1" t="inlineStr">
+        <is>
+          <t>2037-06</t>
+        </is>
+      </c>
+      <c r="FT1" t="inlineStr">
+        <is>
+          <t>2037-07</t>
+        </is>
+      </c>
+      <c r="FU1" t="inlineStr">
+        <is>
+          <t>2037-08</t>
+        </is>
+      </c>
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t>2037-09</t>
+        </is>
+      </c>
+      <c r="FW1" t="inlineStr">
+        <is>
+          <t>2037-10</t>
+        </is>
+      </c>
+      <c r="FX1" t="inlineStr">
+        <is>
+          <t>2037-11</t>
+        </is>
+      </c>
+      <c r="FY1" t="inlineStr">
+        <is>
+          <t>2037-12</t>
+        </is>
+      </c>
+      <c r="FZ1" t="inlineStr">
+        <is>
+          <t>2038-01</t>
+        </is>
+      </c>
+      <c r="GA1" t="inlineStr">
+        <is>
+          <t>2038-02</t>
+        </is>
+      </c>
+      <c r="GB1" t="inlineStr">
+        <is>
+          <t>2038-03</t>
+        </is>
+      </c>
+      <c r="GC1" t="inlineStr">
+        <is>
+          <t>2038-04</t>
+        </is>
+      </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t>2038-05</t>
+        </is>
+      </c>
+      <c r="GE1" t="inlineStr">
+        <is>
+          <t>2038-06</t>
+        </is>
+      </c>
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>2038-07</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>2038-08</t>
+        </is>
+      </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t>2038-09</t>
+        </is>
+      </c>
+      <c r="GI1" t="inlineStr">
+        <is>
+          <t>2038-10</t>
+        </is>
+      </c>
+      <c r="GJ1" t="inlineStr">
+        <is>
+          <t>2038-11</t>
+        </is>
+      </c>
+      <c r="GK1" t="inlineStr">
+        <is>
+          <t>2038-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>custo_total</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>101115.17</v>
+      </c>
+      <c r="V2" t="n">
+        <v>131267.68</v>
+      </c>
+      <c r="W2" t="n">
+        <v>368593.3848637836</v>
+      </c>
+      <c r="X2" t="n">
+        <v>121111.8842068603</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>713169.4339314839</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1539854.56</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1262838.71</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1209587.05</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1189484.152830585</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1135054.626607902</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1977744.526315656</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2411333.168016748</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2271077.361507017</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2361676.657432924</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2476849.703709069</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2671730.809172639</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1929954.284674397</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5598597.617913179</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3175108.746426018</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5308355.458171361</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5761089.073076983</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6238587.512104752</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7093367.230697965</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7596452.167459536</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -90204,13 +90324,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7CBFA72-6ACF-422A-A38C-2B49768919EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37852942-1DB2-496D-9768-B6A17444E9EB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D6C148E-E11C-49DB-A847-6138379621C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D45CA67B-42C3-4AB5-8E57-04927EF62E2F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0115F324-4BED-4747-B8C5-CB1A8BC17501}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63EF740B-4622-49FA-9D16-6CFE537489B0}"/>
 </file>
--- a/empresas/gnlink/analises-financeiras/bp/gnlink-bp-historico.xlsx
+++ b/empresas/gnlink/analises-financeiras/bp/gnlink-bp-historico.xlsx
@@ -64599,7 +64599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL82"/>
+  <dimension ref="A1:AM82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64690,105 +64690,110 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>segmento</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>top</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>margem</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>correcao_mol</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>S1_vol</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>S1_ini</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>S1_fim</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>S2_vol</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>S2_ini</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>S2_fim</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>S3_vol</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>S3_ini</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>S3_fim</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>S4_vol</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>S4_ini</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>S4_fim</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>S5_vol</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>S5_ini</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>S5_fim</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>S6_vol</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>S6_ini</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>S6_fim</t>
         </is>
@@ -64845,86 +64850,91 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>0.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>0.3</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -64981,80 +64991,85 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -65122,80 +65137,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
         <v>2000</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>1300</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>1417</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>2000</v>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -65252,80 +65272,85 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -65393,80 +65418,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
         <v>5000</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>6500</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -65526,80 +65556,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -65667,80 +65702,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
         <v>14000</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -65808,80 +65848,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U9" t="n">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
         <v>3000</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>2028-04</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>2028-06</t>
         </is>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>5000</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>2028-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -65949,80 +65994,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
         <v>2000</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
@@ -66095,80 +66145,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
         <v>2903</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>26500</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>25000</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
@@ -66236,77 +66291,82 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U12" t="n">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
         <v>2000</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="inlineStr">
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>2036-05</t>
         </is>
@@ -66374,80 +66434,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U13" t="n">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
         <v>3000</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="inlineStr">
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>2037-04</t>
         </is>
@@ -66515,80 +66580,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U14" t="n">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
         <v>4500</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="inlineStr">
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AM14" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -66656,80 +66726,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U15" t="n">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
         <v>2000</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>5000</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="inlineStr">
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
+      <c r="AM15" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -66797,80 +66872,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U16" t="n">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
         <v>4000</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>8000</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="inlineStr">
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -66938,80 +67018,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U17" t="n">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
         <v>8000</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="inlineStr">
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AM17" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -67076,80 +67161,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U18" t="n">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
         <v>1049</v>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>2028-02</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>2028-05</t>
         </is>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>2098</v>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>2028-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="inlineStr">
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
@@ -67209,80 +67299,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="inlineStr">
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
+      <c r="AM19" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
@@ -67350,80 +67445,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U20" t="n">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
         <v>464.516129032258</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>800</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>2036-12</t>
         </is>
       </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>2036-12</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>2036-12</t>
         </is>
       </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>2036-12</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>2036-12</t>
         </is>
       </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t>2036-12</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>2036-12</t>
         </is>
       </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="inlineStr">
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="inlineStr">
         <is>
           <t>2036-12</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
+      <c r="AM20" t="inlineStr">
         <is>
           <t>2036-12</t>
         </is>
@@ -67491,80 +67591,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U21" t="n">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
         <v>3000</v>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="inlineStr">
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
+      <c r="AM21" t="inlineStr">
         <is>
           <t>2036-03</t>
         </is>
@@ -67632,80 +67737,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U22" t="n">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
         <v>1049</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>2028-02</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>2028-05</t>
         </is>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>2098</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>2028-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="inlineStr">
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
+      <c r="AM22" t="inlineStr">
         <is>
           <t>2037-03</t>
         </is>
@@ -67776,80 +67886,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U23" t="n">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
         <v>4167.928886952649</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>5500</v>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>8500</v>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="inlineStr">
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
+      <c r="AM23" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
@@ -67920,80 +68035,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U24" t="n">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Posto</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
         <v>1151.579565217391</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>1200</v>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>2000</v>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="inlineStr">
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
+      <c r="AM24" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -68061,80 +68181,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U25" t="n">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
         <v>1096.774193548387</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>3000</v>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>4000</v>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>2037-08</t>
         </is>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>2037-08</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>2037-08</t>
         </is>
       </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
         <is>
           <t>2037-08</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>2037-08</t>
         </is>
       </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="inlineStr">
         <is>
           <t>2037-08</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AM25" t="inlineStr">
         <is>
           <t>2037-08</t>
         </is>
@@ -68197,80 +68322,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="inlineStr">
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="inlineStr">
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
+      <c r="AM26" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
@@ -68338,80 +68468,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="inlineStr">
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="inlineStr">
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
+      <c r="AM27" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -68479,80 +68614,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U28" t="n">
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
         <v>12000</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="AF28" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="inlineStr">
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="AL28" t="inlineStr">
+      <c r="AM28" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
@@ -68620,80 +68760,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U29" t="n">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
         <v>1325</v>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>2027-08</t>
         </is>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>2650</v>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>2027-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL29" t="inlineStr">
+      <c r="AM29" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -68766,80 +68911,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U30" t="n">
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
         <v>30000</v>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>52000</v>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>62000</v>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
         <v>49859.18918918916</v>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>2033-01</t>
         </is>
       </c>
-      <c r="AG30" t="n">
+      <c r="AH30" t="n">
         <v>45859.18918918916</v>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AI30" t="inlineStr">
         <is>
           <t>2033-01</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AJ30" t="inlineStr">
         <is>
           <t>2036-01</t>
         </is>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AK30" t="n">
         <v>40859.18918918916</v>
       </c>
-      <c r="AK30" t="inlineStr">
+      <c r="AL30" t="inlineStr">
         <is>
           <t>2036-01</t>
         </is>
       </c>
-      <c r="AL30" t="inlineStr">
+      <c r="AM30" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -68907,77 +69057,82 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U31" t="n">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
         <v>3125</v>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>3625</v>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>16000</v>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>2033-01</t>
         </is>
       </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="n">
         <v>20000</v>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>2033-01</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>2036-01</t>
         </is>
       </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
         <v>25000</v>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>2036-01</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AK31" t="inlineStr">
+      <c r="AL31" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL31" t="inlineStr">
+      <c r="AM31" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -69040,80 +69195,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="inlineStr">
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="inlineStr">
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="inlineStr">
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr">
+      <c r="AM32" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
@@ -69138,27 +69298,32 @@
           <t>GNL</t>
         </is>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="inlineStr">
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69187,45 +69352,50 @@
       <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="inlineStr">
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>1900-12</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>1900-12</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>1901-12</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>1901-12</t>
         </is>
       </c>
-      <c r="AF34" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>1902-12</t>
         </is>
       </c>
-      <c r="AH34" t="inlineStr">
+      <c r="AI34" t="inlineStr">
         <is>
           <t>1902-12</t>
         </is>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AK34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69254,45 +69424,50 @@
       <c r="H35" t="n">
         <v>1</v>
       </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="inlineStr">
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>1900-12</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>1900-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>1901-12</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>1901-12</t>
         </is>
       </c>
-      <c r="AF35" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>1902-12</t>
         </is>
       </c>
-      <c r="AH35" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>1902-12</t>
         </is>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AK35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69324,45 +69499,50 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="inlineStr">
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>1900-12</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>1900-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>1901-12</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr">
+      <c r="AF36" t="inlineStr">
         <is>
           <t>1901-12</t>
         </is>
       </c>
-      <c r="AF36" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>1902-12</t>
         </is>
       </c>
-      <c r="AH36" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>1902-12</t>
         </is>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AK36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69420,80 +69600,85 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="inlineStr">
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="inlineStr">
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AF37" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
+      <c r="AJ37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="inlineStr">
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AL37" t="inlineStr">
+      <c r="AM37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -69561,80 +69746,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U38" t="n">
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
         <v>1558.674843943535</v>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr">
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AF38" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
+      <c r="AJ38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AL38" t="inlineStr">
+      <c r="AM38" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -69699,80 +69889,85 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U39" t="n">
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
         <v>1548.387096774194</v>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="inlineStr">
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AF39" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
+      <c r="AJ39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="inlineStr">
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr">
+      <c r="AM39" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -69837,80 +70032,85 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U40" t="n">
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
         <v>20000</v>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="inlineStr">
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AF40" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
+      <c r="AJ40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="inlineStr">
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AL40" t="inlineStr">
+      <c r="AM40" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -69978,80 +70178,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U41" t="n">
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
         <v>4000</v>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="AA41" t="n">
+      <c r="AB41" t="n">
         <v>4000</v>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="inlineStr">
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
+      <c r="AJ41" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="inlineStr">
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL41" t="inlineStr">
+      <c r="AM41" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -70119,80 +70324,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U42" t="n">
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
         <v>2200</v>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="inlineStr">
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF42" t="inlineStr">
+      <c r="AG42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
+      <c r="AJ42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="inlineStr">
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL42" t="inlineStr">
+      <c r="AM42" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -70257,80 +70467,85 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U43" t="n">
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
         <v>2000</v>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="X43" t="n">
+      <c r="Y43" t="n">
         <v>3000</v>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>2027-08</t>
         </is>
       </c>
-      <c r="AA43" t="n">
+      <c r="AB43" t="n">
         <v>4000</v>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>2027-08</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>2028-02</t>
         </is>
       </c>
-      <c r="AD43" t="n">
+      <c r="AE43" t="n">
         <v>5000</v>
       </c>
-      <c r="AE43" t="inlineStr">
+      <c r="AF43" t="inlineStr">
         <is>
           <t>2028-02</t>
         </is>
       </c>
-      <c r="AF43" t="inlineStr">
+      <c r="AG43" t="inlineStr">
         <is>
           <t>2028-08</t>
         </is>
       </c>
-      <c r="AG43" t="n">
+      <c r="AH43" t="n">
         <v>6000</v>
       </c>
-      <c r="AH43" t="inlineStr">
+      <c r="AI43" t="inlineStr">
         <is>
           <t>2028-08</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
+      <c r="AJ43" t="inlineStr">
         <is>
           <t>2029-02</t>
         </is>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AK43" t="n">
         <v>11756</v>
       </c>
-      <c r="AK43" t="inlineStr">
+      <c r="AL43" t="inlineStr">
         <is>
           <t>2029-02</t>
         </is>
       </c>
-      <c r="AL43" t="inlineStr">
+      <c r="AM43" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -70395,80 +70610,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U44" t="n">
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
         <v>1435</v>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>2028-02</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>2028-05</t>
         </is>
       </c>
-      <c r="X44" t="n">
+      <c r="Y44" t="n">
         <v>2870</v>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>2028-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="inlineStr">
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AF44" t="inlineStr">
+      <c r="AG44" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
+      <c r="AJ44" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="inlineStr">
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL44" t="inlineStr">
+      <c r="AM44" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -70533,80 +70753,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U45" t="n">
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
         <v>1435</v>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>2028-02</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>2028-05</t>
         </is>
       </c>
-      <c r="X45" t="n">
+      <c r="Y45" t="n">
         <v>2870</v>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>2028-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="inlineStr">
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AF45" t="inlineStr">
+      <c r="AG45" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
+      <c r="AJ45" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="inlineStr">
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL45" t="inlineStr">
+      <c r="AM45" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -70679,77 +70904,82 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U46" t="n">
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
         <v>10000</v>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="X46" t="n">
+      <c r="Y46" t="n">
         <v>20000</v>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="inlineStr">
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AF46" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AJ46" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="inlineStr">
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="AL46" t="inlineStr">
+      <c r="AM46" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
@@ -70822,80 +71052,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U47" t="n">
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
         <v>18740</v>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>2027-05</t>
         </is>
       </c>
-      <c r="X47" t="n">
+      <c r="Y47" t="n">
         <v>13916</v>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>2027-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
         <v>18740</v>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="AD47" t="n">
+      <c r="AE47" t="n">
         <v>25000</v>
       </c>
-      <c r="AE47" t="inlineStr">
+      <c r="AF47" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="AF47" t="inlineStr">
+      <c r="AG47" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>30000</v>
       </c>
-      <c r="AH47" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
+      <c r="AJ47" t="inlineStr">
         <is>
           <t>2031-02</t>
         </is>
       </c>
-      <c r="AJ47" t="n">
+      <c r="AK47" t="n">
         <v>32844.2</v>
       </c>
-      <c r="AK47" t="inlineStr">
+      <c r="AL47" t="inlineStr">
         <is>
           <t>2031-02</t>
         </is>
       </c>
-      <c r="AL47" t="inlineStr">
+      <c r="AM47" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -70960,74 +71195,79 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U48" t="n">
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Posto</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
         <v>2000</v>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="X48" t="n">
+      <c r="Y48" t="n">
         <v>4000.00000000001</v>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AD48" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AE48" t="inlineStr">
+      <c r="AF48" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF48" t="inlineStr">
+      <c r="AG48" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
+      <c r="AJ48" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="inlineStr">
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL48" t="inlineStr">
+      <c r="AM48" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -71100,49 +71340,54 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U49" t="n">
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
         <v>1780.322580645161</v>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="X49" t="n">
+      <c r="Y49" t="n">
         <v>10000</v>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="inlineStr">
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AL49" t="inlineStr">
+      <c r="AM49" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
@@ -71210,80 +71455,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U50" t="n">
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
         <v>1666.666666666667</v>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="X50" t="n">
+      <c r="Y50" t="n">
         <v>2000</v>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="n">
         <v>2258</v>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AD50" t="n">
+      <c r="AE50" t="n">
         <v>3000</v>
       </c>
-      <c r="AE50" t="inlineStr">
+      <c r="AF50" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AF50" t="inlineStr">
+      <c r="AG50" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI50" t="inlineStr">
+      <c r="AJ50" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="inlineStr">
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL50" t="inlineStr">
+      <c r="AM50" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -71351,80 +71601,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U51" t="n">
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
         <v>2500</v>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="X51" t="n">
+      <c r="Y51" t="n">
         <v>5000</v>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>2027-10</t>
         </is>
       </c>
-      <c r="AA51" t="n">
+      <c r="AB51" t="n">
         <v>10000</v>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>2027-10</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="inlineStr">
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF51" t="inlineStr">
+      <c r="AG51" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI51" t="inlineStr">
+      <c r="AJ51" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="inlineStr">
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL51" t="inlineStr">
+      <c r="AM51" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -71489,80 +71744,85 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U52" t="n">
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Posto</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
         <v>2000</v>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="X52" t="n">
+      <c r="Y52" t="n">
         <v>5000</v>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>2028-07</t>
         </is>
       </c>
-      <c r="AA52" t="n">
+      <c r="AB52" t="n">
         <v>10000</v>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>2028-07</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="inlineStr">
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF52" t="inlineStr">
+      <c r="AG52" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI52" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="inlineStr">
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
+      <c r="AM52" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -71622,80 +71882,85 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="inlineStr">
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Posto</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="inlineStr">
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AF53" t="inlineStr">
+      <c r="AG53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AI53" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="inlineStr">
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr">
+      <c r="AM53" t="inlineStr">
         <is>
           <t>2027-12</t>
         </is>
@@ -71755,77 +72020,82 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="inlineStr">
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Posto</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="inlineStr">
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AF54" t="inlineStr">
+      <c r="AG54" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AI54" t="inlineStr">
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="inlineStr">
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AM54" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
@@ -71890,80 +72160,85 @@
           <t>FOB</t>
         </is>
       </c>
-      <c r="U55" t="n">
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Posto</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
         <v>2000</v>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="X55" t="n">
+      <c r="Y55" t="n">
         <v>3000</v>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="AA55" t="n">
+      <c r="AB55" t="n">
         <v>4000</v>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="AD55" t="n">
+      <c r="AE55" t="n">
         <v>4496</v>
       </c>
-      <c r="AE55" t="inlineStr">
+      <c r="AF55" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="AF55" t="inlineStr">
+      <c r="AG55" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AI55" t="inlineStr">
+      <c r="AJ55" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="inlineStr">
+      <c r="AK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr">
+      <c r="AM55" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -71988,27 +72263,32 @@
           <t>GNC</t>
         </is>
       </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="inlineStr">
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72079,77 +72359,82 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U57" t="n">
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
         <v>15000</v>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="X57" t="n">
+      <c r="Y57" t="n">
         <v>8000</v>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AA57" t="n">
+      <c r="AB57" t="n">
         <v>3000</v>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>2030-12</t>
         </is>
       </c>
-      <c r="AE57" t="inlineStr">
+      <c r="AF57" t="inlineStr">
         <is>
           <t>2030-12</t>
         </is>
       </c>
-      <c r="AF57" t="inlineStr">
+      <c r="AG57" t="inlineStr">
         <is>
           <t>2031-01</t>
         </is>
       </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
         <is>
           <t>2031-01</t>
         </is>
       </c>
-      <c r="AI57" t="inlineStr">
+      <c r="AJ57" t="inlineStr">
         <is>
           <t>2031-01</t>
         </is>
       </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="inlineStr">
+      <c r="AK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL57" t="inlineStr">
         <is>
           <t>2031-01</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
+      <c r="AM57" t="inlineStr">
         <is>
           <t>2031-01</t>
         </is>
@@ -72217,80 +72502,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U58" t="n">
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
         <v>9000</v>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="inlineStr">
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF58" t="inlineStr">
+      <c r="AG58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
+      <c r="AJ58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK58" t="inlineStr">
+      <c r="AK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AM58" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -72358,33 +72648,38 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="AF59" t="inlineStr">
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
         <is>
           <t>2030-09</t>
         </is>
       </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
         <is>
           <t>2030-09</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr">
+      <c r="AJ59" t="inlineStr">
         <is>
           <t>2030-09</t>
         </is>
       </c>
-      <c r="AJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK59" t="inlineStr">
+      <c r="AK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="inlineStr">
         <is>
           <t>2030-09</t>
         </is>
       </c>
-      <c r="AL59" t="inlineStr">
+      <c r="AM59" t="inlineStr">
         <is>
           <t>2030-09</t>
         </is>
@@ -72452,71 +72747,76 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U60" t="n">
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
         <v>3325</v>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>2028-12</t>
         </is>
       </c>
-      <c r="X60" t="n">
+      <c r="Y60" t="n">
         <v>4575</v>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>2028-12</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AE60" t="inlineStr">
+      <c r="AF60" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AF60" t="inlineStr">
+      <c r="AG60" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AH60" t="inlineStr">
+      <c r="AI60" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AI60" t="inlineStr">
+      <c r="AJ60" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" t="inlineStr">
+      <c r="AK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL60" t="inlineStr">
+      <c r="AM60" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -72584,80 +72884,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U61" t="n">
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
         <v>5000</v>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="inlineStr">
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF61" t="inlineStr">
+      <c r="AG61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI61" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" t="inlineStr">
+      <c r="AK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL61" t="inlineStr">
+      <c r="AM61" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -72725,80 +73030,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U62" t="n">
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
         <v>71000</v>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="inlineStr">
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AF62" t="inlineStr">
+      <c r="AG62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
+      <c r="AJ62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="inlineStr">
+      <c r="AK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
       </c>
-      <c r="AL62" t="inlineStr">
+      <c r="AM62" t="inlineStr">
         <is>
           <t>2029-12</t>
         </is>
@@ -72871,80 +73181,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U63" t="n">
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
         <v>35000</v>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
+      <c r="AD63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="inlineStr">
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF63" t="inlineStr">
+      <c r="AG63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI63" t="inlineStr">
+      <c r="AJ63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK63" t="inlineStr">
+      <c r="AK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL63" t="inlineStr">
+      <c r="AM63" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -73017,80 +73332,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U64" t="n">
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
         <v>10000</v>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="inlineStr">
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF64" t="inlineStr">
+      <c r="AG64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI64" t="inlineStr">
+      <c r="AJ64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK64" t="inlineStr">
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL64" t="inlineStr">
+      <c r="AM64" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -73163,80 +73483,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U65" t="n">
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
         <v>17000</v>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="X65" t="n">
+      <c r="Y65" t="n">
         <v>30000</v>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>2031-01</t>
         </is>
       </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="inlineStr">
         <is>
           <t>2031-01</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
+      <c r="AD65" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="inlineStr">
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF65" t="inlineStr">
+      <c r="AG65" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI65" t="inlineStr">
+      <c r="AJ65" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK65" t="inlineStr">
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL65" t="inlineStr">
+      <c r="AM65" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -73309,80 +73634,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U66" t="n">
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
         <v>25000</v>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="inlineStr">
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF66" t="inlineStr">
+      <c r="AG66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI66" t="inlineStr">
+      <c r="AJ66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="inlineStr">
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL66" t="inlineStr">
+      <c r="AM66" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -73455,80 +73785,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U67" t="n">
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
         <v>25000</v>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="inlineStr">
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF67" t="inlineStr">
+      <c r="AG67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
+      <c r="AJ67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK67" t="inlineStr">
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL67" t="inlineStr">
+      <c r="AM67" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -73601,80 +73936,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U68" t="n">
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
         <v>21000</v>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
+      <c r="AD68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="inlineStr">
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF68" t="inlineStr">
+      <c r="AG68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI68" t="inlineStr">
+      <c r="AJ68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="inlineStr">
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL68" t="inlineStr">
+      <c r="AM68" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -73747,80 +74087,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U69" t="n">
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
         <v>30000</v>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>2031-02</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="inlineStr">
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF69" t="inlineStr">
+      <c r="AG69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI69" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK69" t="inlineStr">
+      <c r="AK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL69" t="inlineStr">
+      <c r="AM69" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -73888,80 +74233,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U70" t="n">
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
         <v>10000</v>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>2028-07</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="X70" t="n">
+      <c r="Y70" t="n">
         <v>20000</v>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
+      <c r="AD70" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="inlineStr">
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF70" t="inlineStr">
+      <c r="AG70" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr">
+      <c r="AJ70" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK70" t="inlineStr">
+      <c r="AK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL70" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL70" t="inlineStr">
+      <c r="AM70" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -74034,83 +74384,88 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="S71" t="n">
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="T71" t="n">
         <v>0.3</v>
       </c>
-      <c r="U71" t="n">
+      <c r="V71" t="n">
         <v>40000</v>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
+      <c r="AD71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AD71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="inlineStr">
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AF71" t="inlineStr">
+      <c r="AG71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AI71" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AJ71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK71" t="inlineStr">
+      <c r="AK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL71" t="inlineStr">
+      <c r="AM71" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -74178,80 +74533,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U72" t="n">
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
         <v>12000</v>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>2028-07</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
+      <c r="AD72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="inlineStr">
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF72" t="inlineStr">
+      <c r="AG72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI72" t="inlineStr">
+      <c r="AJ72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK72" t="inlineStr">
+      <c r="AK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL72" t="inlineStr">
+      <c r="AM72" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -74319,80 +74679,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U73" t="n">
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
         <v>30000</v>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="X73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="AA73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="inlineStr">
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
+      <c r="AD73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="AD73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="inlineStr">
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="AF73" t="inlineStr">
+      <c r="AG73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="AG73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="AI73" t="inlineStr">
+      <c r="AJ73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="AJ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK73" t="inlineStr">
+      <c r="AK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
       </c>
-      <c r="AL73" t="inlineStr">
+      <c r="AM73" t="inlineStr">
         <is>
           <t>2040-06</t>
         </is>
@@ -74465,80 +74830,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U74" t="n">
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
         <v>20000</v>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>2028-07</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="X74" t="n">
+      <c r="Y74" t="n">
         <v>40000</v>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AA74" t="n">
+      <c r="AB74" t="n">
         <v>110000</v>
       </c>
-      <c r="AB74" t="inlineStr">
+      <c r="AC74" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
+      <c r="AD74" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="inlineStr">
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF74" t="inlineStr">
+      <c r="AG74" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI74" t="inlineStr">
+      <c r="AJ74" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK74" t="inlineStr">
+      <c r="AK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL74" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL74" t="inlineStr">
+      <c r="AM74" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -74611,80 +74981,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U75" t="n">
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
         <v>20000</v>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>2028-07</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="X75" t="n">
+      <c r="Y75" t="n">
         <v>32000</v>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB75" t="inlineStr">
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
+      <c r="AD75" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="inlineStr">
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF75" t="inlineStr">
+      <c r="AG75" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI75" t="inlineStr">
+      <c r="AJ75" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK75" t="inlineStr">
+      <c r="AK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL75" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL75" t="inlineStr">
+      <c r="AM75" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -74757,80 +75132,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U76" t="n">
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
         <v>9000</v>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>2028-07</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="X76" t="n">
+      <c r="Y76" t="n">
         <v>22000</v>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
+      <c r="AD76" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="inlineStr">
+      <c r="AE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AF76" t="inlineStr">
+      <c r="AG76" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AI76" t="inlineStr">
+      <c r="AJ76" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AJ76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK76" t="inlineStr">
+      <c r="AK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL76" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
       </c>
-      <c r="AL76" t="inlineStr">
+      <c r="AM76" t="inlineStr">
         <is>
           <t>2038-12</t>
         </is>
@@ -74898,80 +75278,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U77" t="n">
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
         <v>5000</v>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>2027-07</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="X77" t="n">
+      <c r="Y77" t="n">
         <v>5000</v>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AA77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
+      <c r="AD77" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="inlineStr">
+      <c r="AE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AF77" t="inlineStr">
+      <c r="AG77" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
+      <c r="AJ77" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AJ77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK77" t="inlineStr">
+      <c r="AK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL77" t="inlineStr">
+      <c r="AM77" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -75044,54 +75429,59 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U78" t="n">
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
         <v>4874</v>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>2027-04</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="X78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="inlineStr">
         <is>
           <t>2027-06</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>2032-01</t>
         </is>
       </c>
-      <c r="AA78" t="n">
+      <c r="AB78" t="n">
         <v>5000</v>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AC78" t="inlineStr">
         <is>
           <t>2032-01</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
+      <c r="AD78" t="inlineStr">
         <is>
           <t>2034-12</t>
         </is>
       </c>
-      <c r="AD78" t="n">
+      <c r="AE78" t="n">
         <v>15000</v>
       </c>
-      <c r="AE78" t="inlineStr">
+      <c r="AF78" t="inlineStr">
         <is>
           <t>2034-12</t>
         </is>
       </c>
-      <c r="AF78" t="inlineStr">
+      <c r="AG78" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -75164,77 +75554,82 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U79" t="n">
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
         <v>23000</v>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>2027-05</t>
         </is>
       </c>
-      <c r="X79" t="n">
+      <c r="Y79" t="n">
         <v>30000</v>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>2027-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
+      <c r="AC79" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
+      <c r="AD79" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="inlineStr">
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AF79" t="inlineStr">
+      <c r="AG79" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AI79" t="inlineStr">
+      <c r="AJ79" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AJ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK79" t="inlineStr">
+      <c r="AK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL79" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL79" t="inlineStr">
+      <c r="AM79" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -75307,80 +75702,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U80" t="n">
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
         <v>34000</v>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>2028-12</t>
         </is>
       </c>
-      <c r="X80" t="n">
+      <c r="Y80" t="n">
         <v>41000</v>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>2028-12</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>2029-02</t>
         </is>
       </c>
-      <c r="AA80" t="n">
+      <c r="AB80" t="n">
         <v>45000</v>
       </c>
-      <c r="AB80" t="inlineStr">
+      <c r="AC80" t="inlineStr">
         <is>
           <t>2029-02</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
+      <c r="AD80" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AD80" t="n">
+      <c r="AE80" t="n">
         <v>62141</v>
       </c>
-      <c r="AE80" t="inlineStr">
+      <c r="AF80" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AF80" t="inlineStr">
+      <c r="AG80" t="inlineStr">
         <is>
           <t>2031-02</t>
         </is>
       </c>
-      <c r="AG80" t="n">
+      <c r="AH80" t="n">
         <v>65140.81081081084</v>
       </c>
-      <c r="AH80" t="inlineStr">
+      <c r="AI80" t="inlineStr">
         <is>
           <t>2031-02</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
+      <c r="AJ80" t="inlineStr">
         <is>
           <t>2033-03</t>
         </is>
       </c>
-      <c r="AJ80" t="n">
+      <c r="AK80" t="n">
         <v>69140.81081081084</v>
       </c>
-      <c r="AK80" t="inlineStr">
+      <c r="AL80" t="inlineStr">
         <is>
           <t>2033-03</t>
         </is>
       </c>
-      <c r="AL80" t="inlineStr">
+      <c r="AM80" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -75453,80 +75853,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U81" t="n">
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
         <v>10000</v>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>2028-01</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="X81" t="n">
+      <c r="Y81" t="n">
         <v>20000</v>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>2029-01</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AA81" t="n">
+      <c r="AB81" t="n">
         <v>30000</v>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
+      <c r="AD81" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AD81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="inlineStr">
+      <c r="AE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AF81" t="inlineStr">
+      <c r="AG81" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AG81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
+      <c r="AH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AI81" t="inlineStr">
+      <c r="AJ81" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AJ81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK81" t="inlineStr">
+      <c r="AK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL81" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL81" t="inlineStr">
+      <c r="AM81" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -75594,80 +75999,85 @@
           <t>CIF</t>
         </is>
       </c>
-      <c r="U82" t="n">
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Distribuidora</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
         <v>5000</v>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="W82" t="inlineStr">
         <is>
           <t>2030-01</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
+      <c r="AD82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="inlineStr">
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AF82" t="inlineStr">
+      <c r="AG82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AG82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AI82" t="inlineStr">
+      <c r="AJ82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AJ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK82" t="inlineStr">
+      <c r="AK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
       </c>
-      <c r="AL82" t="inlineStr">
+      <c r="AM82" t="inlineStr">
         <is>
           <t>2037-12</t>
         </is>
@@ -96643,13 +97053,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA71C14A-B039-4860-A539-683FFA2AF8C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{536A47CC-8227-4442-96A6-F43689D7CD91}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D91BB598-34B1-4832-AD9D-6FC5F07A608D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95783C5-75A5-4143-BB28-A4DC210CF9B4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D1BB55E-291A-4927-B9F0-F967014AC313}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C1FA29F-2455-47BB-8126-BE0AB8C6263E}"/>
 </file>